--- a/96/food/2026-01-20-sm.xlsx
+++ b/96/food/2026-01-20-sm.xlsx
@@ -801,7 +801,7 @@
       </c>
       <c r="J1" s="5" t="inlineStr">
         <is>
-          <t>20.01.2026</t>
+          <t>2026-01-20</t>
         </is>
       </c>
     </row>
